--- a/data/menu.xlsx
+++ b/data/menu.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leejonghoo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417D6062-B0D0-FA4C-BC93-609044AD4399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1350A6B-8150-C34E-8FFB-1D33FC92E8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="23260" windowHeight="12460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="용산 인근 50개 식당 메뉴 분석" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'용산 인근 50개 식당 메뉴 분석'!$A$3:$O$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'용산 인근 50개 식당 메뉴 분석'!$A$3:$O$130</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -36,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="258">
-  <si>
-    <t>🏢 삼일회계법인(LS용산타워·아모레퍼시픽본사) 인근 49개 식당 메뉴별 상세 정보 (검증·수정본)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="266">
+  <si>
+    <t>🏢 삼일회계법인(LS용산타워·아모레퍼시픽본사) 인근 50개 식당 메뉴별 상세 정보 (검증·수정본)</t>
   </si>
   <si>
     <t>검증상태: 확인=검색으로 확인 / 부분확인=타 지점·단일 출처 / 미확인=원본 값 유지. 영양값은 모두 추정치이며 공식값 표기는 원본 그대로입니다. / 하늘색 셀=영양값 재추정·수정(변경내역 시트 참조).</t>
@@ -809,7 +809,32 @@
     <t>카레당면</t>
   </si>
   <si>
-    <t>갈비당면</t>
+    <t>슬로우캘리 신용산점</t>
+  </si>
+  <si>
+    <t>연어 포케 (메밀면&amp;샐러드)</t>
+  </si>
+  <si>
+    <t>평일 20:30 라스트오더</t>
+  </si>
+  <si>
+    <t>블랙페퍼 치킨 보울 (현미밥&amp;샐러드)</t>
+  </si>
+  <si>
+    <t>부채살 스테이크 보울 (현미밥&amp;샐러드)</t>
+  </si>
+  <si>
+    <t>탄단지데이 샐러드</t>
+  </si>
+  <si>
+    <t>비프&amp;치킨 더블프로틴 보울 (현미밥&amp;샐러드)</t>
+  </si>
+  <si>
+    <t>니모메 신용산점</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>니모메</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1285,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1316,7 +1341,7 @@
       <c r="N1" s="23"/>
       <c r="O1" s="23"/>
     </row>
-    <row r="2" spans="1:15" ht="17.25" customHeight="1">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6020,7 +6045,7 @@
         <v>24</v>
       </c>
       <c r="O100" s="11">
-        <f t="shared" ref="O100:O125" si="3">J100*4+K100*4+L100*9</f>
+        <f t="shared" ref="O100:O130" si="3">J100*4+K100*4+L100*9</f>
         <v>838</v>
       </c>
     </row>
@@ -7225,20 +7250,20 @@
       </c>
     </row>
     <row r="126" spans="1:15" ht="19.5" customHeight="1">
-      <c r="A126" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>248</v>
+      <c r="A126" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D126" s="6">
-        <v>3900</v>
+        <v>12900</v>
       </c>
       <c r="E126" s="6">
-        <v>354</v>
+        <v>536.29999999999995</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>233</v>
@@ -7250,35 +7275,275 @@
         <v>21</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J126" s="6">
-        <v>70</v>
+        <v>52.8</v>
       </c>
       <c r="K126" s="6">
-        <v>4</v>
+        <v>30.5</v>
       </c>
       <c r="L126" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M126" s="14" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="N126" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O126" s="15">
-        <f t="shared" ref="O126" si="4">J126*4+K126*4+L126*9</f>
-        <v>350</v>
+      <c r="O126" s="11">
+        <f t="shared" si="3"/>
+        <v>414.2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A127" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D127" s="6">
+        <v>12500</v>
+      </c>
+      <c r="E127" s="6">
+        <v>725.7</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J127" s="6">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="K127" s="6">
+        <v>49.7</v>
+      </c>
+      <c r="L127" s="6">
+        <v>27</v>
+      </c>
+      <c r="M127" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N127" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O127" s="11">
+        <f t="shared" si="3"/>
+        <v>719.40000000000009</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A128" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D128" s="6">
+        <v>14500</v>
+      </c>
+      <c r="E128" s="6">
+        <v>645.5</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J128" s="6">
+        <v>63.4</v>
+      </c>
+      <c r="K128" s="6">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="L128" s="6">
+        <v>16.2</v>
+      </c>
+      <c r="M128" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N128" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O128" s="11">
+        <f t="shared" si="3"/>
+        <v>552.19999999999993</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A129" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D129" s="6">
+        <v>8500</v>
+      </c>
+      <c r="E129" s="6">
+        <v>287.60000000000002</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J129" s="6">
+        <v>23.9</v>
+      </c>
+      <c r="K129" s="6">
+        <v>20.5</v>
+      </c>
+      <c r="L129" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="M129" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N129" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O129" s="11">
+        <f t="shared" si="3"/>
+        <v>287.39999999999998</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A130" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D130" s="6">
+        <v>16900</v>
+      </c>
+      <c r="E130" s="6">
+        <v>750.9</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J130" s="6">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="K130" s="6">
+        <v>56.2</v>
+      </c>
+      <c r="L130" s="6">
+        <v>32.4</v>
+      </c>
+      <c r="M130" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N130" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O130" s="11">
+        <f t="shared" si="3"/>
+        <v>794</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A131" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D131" s="6">
+        <v>16900</v>
+      </c>
+      <c r="E131" s="6">
+        <v>750.9</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J131" s="6">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="K131" s="6">
+        <v>56.2</v>
+      </c>
+      <c r="L131" s="6">
+        <v>32.4</v>
+      </c>
+      <c r="M131" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N131" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O131" s="11">
+        <f t="shared" ref="O131" si="4">J131*4+K131*4+L131*9</f>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O125" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:O130" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="O4:O126">
+  <conditionalFormatting sqref="O4:O131">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>ABS(O4-E4)/E4&gt;0.15</formula>
     </cfRule>

--- a/data/menu.xlsx
+++ b/data/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leejonghoo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1350A6B-8150-C34E-8FFB-1D33FC92E8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB555D94-B32B-184C-85A2-DB32B2337A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="23260" windowHeight="12460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="264">
   <si>
     <t>🏢 삼일회계법인(LS용산타워·아모레퍼시픽본사) 인근 50개 식당 메뉴별 상세 정보 (검증·수정본)</t>
   </si>
@@ -828,14 +828,6 @@
   </si>
   <si>
     <t>비프&amp;치킨 더블프로틴 보울 (현미밥&amp;샐러드)</t>
-  </si>
-  <si>
-    <t>니모메 신용산점</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>니모메</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1310,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -7489,61 +7481,13 @@
         <v>794</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="19.5" customHeight="1">
-      <c r="A131" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D131" s="6">
-        <v>16900</v>
-      </c>
-      <c r="E131" s="6">
-        <v>750.9</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I131" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J131" s="6">
-        <v>69.400000000000006</v>
-      </c>
-      <c r="K131" s="6">
-        <v>56.2</v>
-      </c>
-      <c r="L131" s="6">
-        <v>32.4</v>
-      </c>
-      <c r="M131" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="N131" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O131" s="11">
-        <f t="shared" ref="O131" si="4">J131*4+K131*4+L131*9</f>
-        <v>794</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A3:O130" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="O4:O131">
+  <conditionalFormatting sqref="O4:O130">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>ABS(O4-E4)/E4&gt;0.15</formula>
     </cfRule>
